--- a/client_gamedata/dialog.xlsx
+++ b/client_gamedata/dialog.xlsx
@@ -36510,7 +36510,7 @@
         <v>fest_022_001_dialog_korean.dialog</v>
       </c>
       <c r="C1806">
-        <v>20474</v>
+        <v>20472</v>
       </c>
       <c r="D1806" t="str">
         <v/>
@@ -36519,7 +36519,7 @@
         <v>1</v>
       </c>
       <c r="F1806" t="str">
-        <v>622aba7301b181731ba57897e45035dfbf4c8dfd2143321b8c0a7c83d865306f</v>
+        <v>2219bae28b6d32ff26eb13c5cb93bedd996520281edfdd894ca2d88e8ca3f354</v>
       </c>
     </row>
     <row r="1807">
